--- a/Output/Models/Exposure_models_malf_card_bin_div10_Femenino.xlsx
+++ b/Output/Models/Exposure_models_malf_card_bin_div10_Femenino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.024200367252293</v>
+        <v>1.025925103541832</v>
       </c>
       <c r="C3">
-        <v>0.05385086435303259</v>
+        <v>0.05486534335480903</v>
       </c>
       <c r="D3">
-        <v>0.44404447186343</v>
+        <v>0.4665011466582726</v>
       </c>
       <c r="E3">
-        <v>0.6570104314994668</v>
+        <v>0.6408568270088513</v>
       </c>
       <c r="F3">
-        <v>0.9216095966645406</v>
+        <v>0.9213278342562596</v>
       </c>
       <c r="G3">
-        <v>1.138211229653195</v>
+        <v>1.142397178228058</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.960937684425905</v>
+        <v>0.9599835623478813</v>
       </c>
       <c r="C4">
-        <v>0.05444744814042838</v>
+        <v>0.05619445721766757</v>
       </c>
       <c r="D4">
-        <v>-0.7318197268227663</v>
+        <v>-0.7267463597512639</v>
       </c>
       <c r="E4">
-        <v>0.464278606897566</v>
+        <v>0.4673813481027985</v>
       </c>
       <c r="F4">
-        <v>0.8636732591099834</v>
+        <v>0.8598664181785476</v>
       </c>
       <c r="G4">
-        <v>1.069155752606474</v>
+        <v>1.071757682932058</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9907529880459252</v>
+        <v>0.9620361463293507</v>
       </c>
       <c r="C5">
-        <v>0.05603860183834826</v>
+        <v>0.05864652607124451</v>
       </c>
       <c r="D5">
-        <v>-0.1657791355954505</v>
+        <v>-0.6599411332287553</v>
       </c>
       <c r="E5">
-        <v>0.8683307662872495</v>
+        <v>0.5092916065087809</v>
       </c>
       <c r="F5">
-        <v>0.8876980103007813</v>
+        <v>0.8575735476263506</v>
       </c>
       <c r="G5">
-        <v>1.105771863777563</v>
+        <v>1.079223524799624</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="6">
@@ -879,22 +879,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.228488065456373</v>
+        <v>1.249191405147895</v>
       </c>
       <c r="C9">
-        <v>0.3366804171264623</v>
+        <v>0.3437707815300382</v>
       </c>
       <c r="D9">
-        <v>0.6112152288512407</v>
+        <v>0.6472233187700663</v>
       </c>
       <c r="E9">
-        <v>0.5410571027899548</v>
+        <v>0.5174874214231164</v>
       </c>
       <c r="F9">
-        <v>0.6350209467255672</v>
+        <v>0.6368113095626887</v>
       </c>
       <c r="G9">
-        <v>2.376587630299</v>
+        <v>2.450457683873399</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -942,22 +942,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.7916580857635477</v>
+        <v>0.7782162838275859</v>
       </c>
       <c r="C10">
-        <v>0.3403632134413239</v>
+        <v>0.3518111781041975</v>
       </c>
       <c r="D10">
-        <v>-0.6864011181280083</v>
+        <v>-0.7127425427792111</v>
       </c>
       <c r="E10">
-        <v>0.4924601995896702</v>
+        <v>0.4760050858571465</v>
       </c>
       <c r="F10">
-        <v>0.4062748693773205</v>
+        <v>0.3905153382037984</v>
       </c>
       <c r="G10">
-        <v>1.542607165723429</v>
+        <v>1.550824065451591</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9523418325707963</v>
+        <v>0.8223494850072548</v>
       </c>
       <c r="C11">
-        <v>0.3472358896362812</v>
+        <v>0.3607252597988556</v>
       </c>
       <c r="D11">
-        <v>-0.1406284381055163</v>
+        <v>-0.542212680501843</v>
       </c>
       <c r="E11">
-        <v>0.8881634811277813</v>
+        <v>0.5876720008107668</v>
       </c>
       <c r="F11">
-        <v>0.4821977021269434</v>
+        <v>0.4055146298388914</v>
       </c>
       <c r="G11">
-        <v>1.880877826799634</v>
+        <v>1.667655432703799</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="O11">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="12">
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.185595577578397</v>
+        <v>1.197475948188544</v>
       </c>
       <c r="C15">
-        <v>0.3116807062444394</v>
+        <v>0.3181158131005787</v>
       </c>
       <c r="D15">
-        <v>0.546216823913776</v>
+        <v>0.5665105526339946</v>
       </c>
       <c r="E15">
-        <v>0.5849169028294467</v>
+        <v>0.5710467614049222</v>
       </c>
       <c r="F15">
-        <v>0.6436258413090231</v>
+        <v>0.6419277172985193</v>
       </c>
       <c r="G15">
-        <v>2.183934800869137</v>
+        <v>2.23381637503466</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.7788533382620056</v>
+        <v>0.7788523082138105</v>
       </c>
       <c r="C16">
-        <v>0.3182134097802422</v>
+        <v>0.3284172170355646</v>
       </c>
       <c r="D16">
-        <v>-0.7854242228475352</v>
+        <v>-0.7610253958425588</v>
       </c>
       <c r="E16">
-        <v>0.4322048832270651</v>
+        <v>0.4466418987023424</v>
       </c>
       <c r="F16">
-        <v>0.4174379607898957</v>
+        <v>0.4091719646290135</v>
       </c>
       <c r="G16">
-        <v>1.453180063868675</v>
+        <v>1.482532945677205</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9893001658999613</v>
+        <v>0.8461075178159254</v>
       </c>
       <c r="C17">
-        <v>0.3249426736546709</v>
+        <v>0.3403215735397048</v>
       </c>
       <c r="D17">
-        <v>-0.03310580551853404</v>
+        <v>-0.4910321614233059</v>
       </c>
       <c r="E17">
-        <v>0.973590213154816</v>
+        <v>0.6234037006723654</v>
       </c>
       <c r="F17">
-        <v>0.523282699591314</v>
+        <v>0.4342534778035915</v>
       </c>
       <c r="G17">
-        <v>1.870336663172834</v>
+        <v>1.648571556238451</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="O17">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="18">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.000321749118175</v>
+        <v>1.000598859925021</v>
       </c>
       <c r="C21">
-        <v>0.03069950581299173</v>
+        <v>0.03122618412253313</v>
       </c>
       <c r="D21">
-        <v>0.01047891031167656</v>
+        <v>0.01917239319491519</v>
       </c>
       <c r="E21">
-        <v>0.9916391922618735</v>
+        <v>0.9847035805932014</v>
       </c>
       <c r="F21">
-        <v>0.9419074775710383</v>
+        <v>0.9411963354958737</v>
       </c>
       <c r="G21">
-        <v>1.062358698265431</v>
+        <v>1.063750506376298</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9628793128892196</v>
+        <v>0.9596157190479664</v>
       </c>
       <c r="C22">
-        <v>0.03188581572775074</v>
+        <v>0.03288778459012536</v>
       </c>
       <c r="D22">
-        <v>-1.186333116370209</v>
+        <v>-1.25342487585781</v>
       </c>
       <c r="E22">
-        <v>0.2354907734666697</v>
+        <v>0.2100511231089223</v>
       </c>
       <c r="F22">
-        <v>0.9045458815303469</v>
+        <v>0.8997113937955622</v>
       </c>
       <c r="G22">
-        <v>1.024974619995449</v>
+        <v>1.023508576855024</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9662822563149469</v>
+        <v>0.9500143373849813</v>
       </c>
       <c r="C23">
-        <v>0.03320118304935165</v>
+        <v>0.03534002702733017</v>
       </c>
       <c r="D23">
-        <v>-1.033074532188556</v>
+        <v>-1.45099500002042</v>
       </c>
       <c r="E23">
-        <v>0.3015690206411341</v>
+        <v>0.1467812524935261</v>
       </c>
       <c r="F23">
-        <v>0.9054054544290687</v>
+        <v>0.8864386304069436</v>
       </c>
       <c r="G23">
-        <v>1.031252235450557</v>
+        <v>1.01814971762083</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="24">
@@ -2013,22 +2013,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.207667859729463</v>
+        <v>1.22313517713902</v>
       </c>
       <c r="C27">
-        <v>0.3131046647216643</v>
+        <v>0.3194798372092501</v>
       </c>
       <c r="D27">
-        <v>0.602645480607727</v>
+        <v>0.630454120351488</v>
       </c>
       <c r="E27">
-        <v>0.5467445576211738</v>
+        <v>0.5283975112542494</v>
       </c>
       <c r="F27">
-        <v>0.6537810594253911</v>
+        <v>0.653932204999136</v>
       </c>
       <c r="G27">
-        <v>2.230810511251862</v>
+        <v>2.287790156407543</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.7491834185691768</v>
+        <v>0.7220926014261774</v>
       </c>
       <c r="C28">
-        <v>0.320709592163219</v>
+        <v>0.3318176809132763</v>
       </c>
       <c r="D28">
-        <v>-0.9004141063927118</v>
+        <v>-0.9812674556533132</v>
       </c>
       <c r="E28">
-        <v>0.3678999165551873</v>
+        <v>0.3264608670495633</v>
       </c>
       <c r="F28">
-        <v>0.399576240982689</v>
+        <v>0.3768332129042186</v>
       </c>
       <c r="G28">
-        <v>1.404677598644597</v>
+        <v>1.383683038487787</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.8440414178202686</v>
+        <v>0.7488163213440776</v>
       </c>
       <c r="C29">
-        <v>0.3287131993519987</v>
+        <v>0.3424134035868553</v>
       </c>
       <c r="D29">
-        <v>-0.5158104775765453</v>
+        <v>-0.844772880849436</v>
       </c>
       <c r="E29">
-        <v>0.6059867839650195</v>
+        <v>0.3982376588038473</v>
       </c>
       <c r="F29">
-        <v>0.4431620633636771</v>
+        <v>0.3827476071313365</v>
       </c>
       <c r="G29">
-        <v>1.607551669898737</v>
+        <v>1.465001668629292</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="O29">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="30">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.048135066023784</v>
+        <v>1.051019241711702</v>
       </c>
       <c r="C33">
-        <v>0.2104841361815141</v>
+        <v>0.2146273398080962</v>
       </c>
       <c r="D33">
-        <v>0.2233539222533564</v>
+        <v>0.2318455783649879</v>
       </c>
       <c r="E33">
-        <v>0.8232600631674066</v>
+        <v>0.8166579549641054</v>
       </c>
       <c r="F33">
-        <v>0.6938296089644165</v>
+        <v>0.6901119443298878</v>
       </c>
       <c r="G33">
-        <v>1.583367302915181</v>
+        <v>1.600669942788585</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2454,22 +2454,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.7763223770986791</v>
+        <v>0.7577935447746529</v>
       </c>
       <c r="C34">
-        <v>0.2194994863562763</v>
+        <v>0.2269549801899028</v>
       </c>
       <c r="D34">
-        <v>-1.15347609630133</v>
+        <v>-1.222023410007885</v>
       </c>
       <c r="E34">
-        <v>0.248715023370865</v>
+        <v>0.2216987743444407</v>
       </c>
       <c r="F34">
-        <v>0.5048981776028594</v>
+        <v>0.485698175489003</v>
       </c>
       <c r="G34">
-        <v>1.193659355328857</v>
+        <v>1.182320802263619</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2517,22 +2517,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.8269856088520726</v>
+        <v>0.7544306911674851</v>
       </c>
       <c r="C35">
-        <v>0.2272805139938051</v>
+        <v>0.2402541977798263</v>
       </c>
       <c r="D35">
-        <v>-0.8358305003874368</v>
+        <v>-1.172890497692474</v>
       </c>
       <c r="E35">
-        <v>0.4032502652430139</v>
+        <v>0.2408397206076992</v>
       </c>
       <c r="F35">
-        <v>0.5297078729240782</v>
+        <v>0.4711016266576068</v>
       </c>
       <c r="G35">
-        <v>1.291098796536966</v>
+        <v>1.208158994936171</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="O35">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="36">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.9595473463439146</v>
+        <v>0.9737371779749754</v>
       </c>
       <c r="C39">
-        <v>0.1227803613918108</v>
+        <v>0.125748366509647</v>
       </c>
       <c r="D39">
-        <v>-0.3363210490263802</v>
+        <v>-0.2116437000266364</v>
       </c>
       <c r="E39">
-        <v>0.7366287786567822</v>
+        <v>0.8323850138285903</v>
       </c>
       <c r="F39">
-        <v>0.7543199181900947</v>
+        <v>0.7610348561859822</v>
       </c>
       <c r="G39">
-        <v>1.22061089422753</v>
+        <v>1.245887864482985</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.006458837692083</v>
+        <v>1.067124496800177</v>
       </c>
       <c r="C40">
-        <v>0.1277165872044905</v>
+        <v>0.1254612643000374</v>
       </c>
       <c r="D40">
-        <v>0.05040902612223392</v>
+        <v>0.5178303053413974</v>
       </c>
       <c r="E40">
-        <v>0.9597964437271316</v>
+        <v>0.6045766720027378</v>
       </c>
       <c r="F40">
-        <v>0.7835802147754471</v>
+        <v>0.8344921734266995</v>
       </c>
       <c r="G40">
-        <v>1.292732221753182</v>
+        <v>1.364607995057556</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.260927601735546</v>
+        <v>1.148237627929189</v>
       </c>
       <c r="C41">
-        <v>0.1254710043727733</v>
+        <v>0.1319571682440382</v>
       </c>
       <c r="D41">
-        <v>1.847818490970882</v>
+        <v>1.047523763099602</v>
       </c>
       <c r="E41">
-        <v>0.06462860501108247</v>
+        <v>0.2948580782072334</v>
       </c>
       <c r="F41">
-        <v>0.9860275262163987</v>
+        <v>0.8865630551352212</v>
       </c>
       <c r="G41">
-        <v>1.612468591946409</v>
+        <v>1.487147070426204</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="42">
@@ -3147,22 +3147,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.7786364591298072</v>
+        <v>0.8959382827827971</v>
       </c>
       <c r="C45">
-        <v>0.7857171665237729</v>
+        <v>0.8033951597492078</v>
       </c>
       <c r="D45">
-        <v>-0.3184492194403694</v>
+        <v>-0.1367742235796795</v>
       </c>
       <c r="E45">
-        <v>0.7501442081654027</v>
+        <v>0.8912092587408967</v>
       </c>
       <c r="F45">
-        <v>0.1669287228757032</v>
+        <v>0.1855354467358731</v>
       </c>
       <c r="G45">
-        <v>3.631937781837835</v>
+        <v>4.326426139467101</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.108550158671746</v>
+        <v>1.399830419598242</v>
       </c>
       <c r="C46">
-        <v>0.8206620366992005</v>
+        <v>0.7868245938429606</v>
       </c>
       <c r="D46">
-        <v>0.1255730051862267</v>
+        <v>0.4274791396432286</v>
       </c>
       <c r="E46">
-        <v>0.9000699325150805</v>
+        <v>0.6690303758600111</v>
       </c>
       <c r="F46">
-        <v>0.2219251675109621</v>
+        <v>0.2994533103228275</v>
       </c>
       <c r="G46">
-        <v>5.537377612795771</v>
+        <v>6.543675211070838</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3273,22 +3273,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>3.709900960192896</v>
+        <v>2.581369047325122</v>
       </c>
       <c r="C47">
-        <v>0.779416790456539</v>
+        <v>0.8180145653645253</v>
       </c>
       <c r="D47">
-        <v>1.682033537062123</v>
+        <v>1.159294634650204</v>
       </c>
       <c r="E47">
-        <v>0.09256233687518678</v>
+        <v>0.2463361080084884</v>
       </c>
       <c r="F47">
-        <v>0.8052329557978228</v>
+        <v>0.519463261319879</v>
       </c>
       <c r="G47">
-        <v>17.09240168989788</v>
+        <v>12.82759851304466</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="O47">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="48">
@@ -3525,22 +3525,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.8332510217204865</v>
+        <v>0.9069310395547036</v>
       </c>
       <c r="C51">
-        <v>0.7001386820227882</v>
+        <v>0.7197143470431413</v>
       </c>
       <c r="D51">
-        <v>-0.2605488602355209</v>
+        <v>-0.1357328272262911</v>
       </c>
       <c r="E51">
-        <v>0.7944404312949993</v>
+        <v>0.8920324954942824</v>
       </c>
       <c r="F51">
-        <v>0.2112597338191755</v>
+        <v>0.2212851666351791</v>
       </c>
       <c r="G51">
-        <v>3.28651017705303</v>
+        <v>3.717031389925136</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.9633830384026234</v>
+        <v>1.365539767382753</v>
       </c>
       <c r="C52">
-        <v>0.7301633839469625</v>
+        <v>0.717850483699019</v>
       </c>
       <c r="D52">
-        <v>-0.05109019671111754</v>
+        <v>0.4340037257454545</v>
       </c>
       <c r="E52">
-        <v>0.9592536476835927</v>
+        <v>0.6642857355254321</v>
       </c>
       <c r="F52">
-        <v>0.2302940919302098</v>
+        <v>0.3344020357967491</v>
       </c>
       <c r="G52">
-        <v>4.030094176116041</v>
+        <v>5.576218613205799</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="B53">
-        <v>3.98620450748865</v>
+        <v>2.456395056071592</v>
       </c>
       <c r="C53">
-        <v>0.7125160051386722</v>
+        <v>0.7466485115811444</v>
       </c>
       <c r="D53">
-        <v>1.940783809691487</v>
+        <v>1.203638441461011</v>
       </c>
       <c r="E53">
-        <v>0.05228450562048825</v>
+        <v>0.2287293547008082</v>
       </c>
       <c r="F53">
-        <v>0.9864267767547081</v>
+        <v>0.5685253697539284</v>
       </c>
       <c r="G53">
-        <v>16.10847023820615</v>
+        <v>10.61320565888655</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="O53">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="54">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9531916578291098</v>
+        <v>0.9567958601505719</v>
       </c>
       <c r="C57">
-        <v>0.05579877505731289</v>
+        <v>0.05643003041774816</v>
       </c>
       <c r="D57">
-        <v>-0.8591458414550135</v>
+        <v>-0.7826545942627412</v>
       </c>
       <c r="E57">
-        <v>0.3902600587858035</v>
+        <v>0.4338299726656974</v>
       </c>
       <c r="F57">
-        <v>0.8544452294879459</v>
+        <v>0.8566155594020751</v>
       </c>
       <c r="G57">
-        <v>1.063350002082052</v>
+        <v>1.068692143112916</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.9571590741564248</v>
+        <v>0.969762831792086</v>
       </c>
       <c r="C58">
-        <v>0.05820330141174841</v>
+        <v>0.05793895485334811</v>
       </c>
       <c r="D58">
-        <v>-0.7522885917358766</v>
+        <v>-0.5299325948381159</v>
       </c>
       <c r="E58">
-        <v>0.4518775269415411</v>
+        <v>0.5961586660122675</v>
       </c>
       <c r="F58">
-        <v>0.8539675750825619</v>
+        <v>0.8656609104226667</v>
       </c>
       <c r="G58">
-        <v>1.072819999227032</v>
+        <v>1.086383754426693</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.9965544045837189</v>
+        <v>0.9587855090009864</v>
       </c>
       <c r="C59">
-        <v>0.05655451274324647</v>
+        <v>0.06234553049577567</v>
       </c>
       <c r="D59">
-        <v>-0.06103041090085626</v>
+        <v>-0.6750746987663365</v>
       </c>
       <c r="E59">
-        <v>0.9513349897932626</v>
+        <v>0.4996283074464435</v>
       </c>
       <c r="F59">
-        <v>0.8919935714782973</v>
+        <v>0.8485019597998775</v>
       </c>
       <c r="G59">
-        <v>1.113372016402894</v>
+        <v>1.083403098429017</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="60">
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.8440768207548451</v>
+        <v>0.9321254282319534</v>
       </c>
       <c r="C63">
-        <v>0.6709266151967078</v>
+        <v>0.6817107586460444</v>
       </c>
       <c r="D63">
-        <v>-0.2526532184549337</v>
+        <v>-0.1031051553934039</v>
       </c>
       <c r="E63">
-        <v>0.8005362014171225</v>
+        <v>0.9178795134207741</v>
       </c>
       <c r="F63">
-        <v>0.2266147656592877</v>
+        <v>0.2450197575755759</v>
       </c>
       <c r="G63">
-        <v>3.143950824487711</v>
+        <v>3.546072457804163</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.7701961938672859</v>
+        <v>0.8762089803854861</v>
       </c>
       <c r="C64">
-        <v>0.7042676146009774</v>
+        <v>0.6871445031036577</v>
       </c>
       <c r="D64">
-        <v>-0.370753949132542</v>
+        <v>-0.1923185790126754</v>
       </c>
       <c r="E64">
-        <v>0.7108208038357351</v>
+        <v>0.8474926660873632</v>
       </c>
       <c r="F64">
-        <v>0.1936991378652751</v>
+        <v>0.2278815887162687</v>
       </c>
       <c r="G64">
-        <v>3.06249260365964</v>
+        <v>3.36903995462343</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4407,22 +4407,22 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.719375846343099</v>
+        <v>1.354083190732803</v>
       </c>
       <c r="C65">
-        <v>0.6688257403988609</v>
+        <v>0.7124986284526394</v>
       </c>
       <c r="D65">
-        <v>0.8103177138669693</v>
+        <v>0.4254388727448545</v>
       </c>
       <c r="E65">
-        <v>0.4177575970734104</v>
+        <v>0.6705167734910319</v>
       </c>
       <c r="F65">
-        <v>0.4635166287299662</v>
+        <v>0.3350930456609897</v>
       </c>
       <c r="G65">
-        <v>6.377879708627006</v>
+        <v>5.471737808847589</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="O65">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="66">
@@ -4659,22 +4659,22 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.746889604803142</v>
+        <v>0.7694047986328055</v>
       </c>
       <c r="C69">
-        <v>0.404995995594407</v>
+        <v>0.4116541093037599</v>
       </c>
       <c r="D69">
-        <v>-0.7205945063160017</v>
+        <v>-0.6367920200680408</v>
       </c>
       <c r="E69">
-        <v>0.471159034871911</v>
+        <v>0.5242603246748641</v>
       </c>
       <c r="F69">
-        <v>0.3376938866173009</v>
+        <v>0.3433636188218464</v>
       </c>
       <c r="G69">
-        <v>1.651922358888252</v>
+        <v>1.724072416846054</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4722,22 +4722,22 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.7212203949153095</v>
+        <v>0.7937083283294391</v>
       </c>
       <c r="C70">
-        <v>0.4232834874023185</v>
+        <v>0.4209144925276782</v>
       </c>
       <c r="D70">
-        <v>-0.7720842381995261</v>
+        <v>-0.5488982536771216</v>
       </c>
       <c r="E70">
-        <v>0.4400645368975917</v>
+        <v>0.5830752766868087</v>
       </c>
       <c r="F70">
-        <v>0.3146070436222099</v>
+        <v>0.3478386779420687</v>
       </c>
       <c r="G70">
-        <v>1.653360497123575</v>
+        <v>1.811106557173703</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.062417118851424</v>
+        <v>0.8568112532233184</v>
       </c>
       <c r="C71">
-        <v>0.4035682332784773</v>
+        <v>0.4457918598626522</v>
       </c>
       <c r="D71">
-        <v>0.1500281934855627</v>
+        <v>-0.3466586984524962</v>
       </c>
       <c r="E71">
-        <v>0.8807423718119105</v>
+        <v>0.7288477421072059</v>
       </c>
       <c r="F71">
-        <v>0.481700566384454</v>
+        <v>0.3576238240448292</v>
       </c>
       <c r="G71">
-        <v>2.34321944626426</v>
+        <v>2.052786962979538</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="O71">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="72">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.8020325533709327</v>
+        <v>0.78429145421059</v>
       </c>
       <c r="C74">
-        <v>0.1094835909802028</v>
+        <v>0.1153774295210812</v>
       </c>
       <c r="D74">
-        <v>-2.014969364141554</v>
+        <v>-2.105910799916571</v>
       </c>
       <c r="E74">
-        <v>0.04390785916276886</v>
+        <v>0.03521210137024858</v>
       </c>
       <c r="F74">
-        <v>0.6471417134093032</v>
+        <v>0.6255586544399888</v>
       </c>
       <c r="G74">
-        <v>0.9939959105369125</v>
+        <v>0.9833020145783485</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.163808666048873</v>
+        <v>1.073254487562039</v>
       </c>
       <c r="C75">
-        <v>0.1042587938676426</v>
+        <v>0.1065473892203392</v>
       </c>
       <c r="D75">
-        <v>1.455013566950519</v>
+        <v>0.6635132959536735</v>
       </c>
       <c r="E75">
-        <v>0.1456655056169008</v>
+        <v>0.5070018668776917</v>
       </c>
       <c r="F75">
-        <v>0.9487162523971386</v>
+        <v>0.8709824634693732</v>
       </c>
       <c r="G75">
-        <v>1.42766671040803</v>
+        <v>1.322501018543823</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.7755162987980485</v>
+        <v>0.7654097974780454</v>
       </c>
       <c r="C76">
-        <v>0.1140201065536213</v>
+        <v>0.1191521728461219</v>
       </c>
       <c r="D76">
-        <v>-2.229661830031128</v>
+        <v>-2.243718257240101</v>
       </c>
       <c r="E76">
-        <v>0.02576990171824776</v>
+        <v>0.02485053466533184</v>
       </c>
       <c r="F76">
-        <v>0.6202072505020042</v>
+        <v>0.6059984364311538</v>
       </c>
       <c r="G76">
-        <v>0.9697170247761888</v>
+        <v>0.9667552304682223</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.087478507178347</v>
+        <v>1.033436849640454</v>
       </c>
       <c r="C77">
-        <v>0.1040512952579403</v>
+        <v>0.1109397944986345</v>
       </c>
       <c r="D77">
-        <v>0.8059651738437946</v>
+        <v>0.2964670614872588</v>
       </c>
       <c r="E77">
-        <v>0.4202629300862172</v>
+        <v>0.7668734180246609</v>
       </c>
       <c r="F77">
-        <v>0.8868538572307423</v>
+        <v>0.8314800222522833</v>
       </c>
       <c r="G77">
-        <v>1.333488594465406</v>
+        <v>1.284446641666566</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="O77">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="78">
@@ -5226,22 +5226,22 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.2329712636030821</v>
+        <v>0.1746976298491037</v>
       </c>
       <c r="C78">
-        <v>0.7893890943845927</v>
+        <v>0.7995505114582948</v>
       </c>
       <c r="D78">
-        <v>-1.845528618980782</v>
+        <v>-2.182099321941645</v>
       </c>
       <c r="E78">
-        <v>0.06496067931806244</v>
+        <v>0.02910220324723643</v>
       </c>
       <c r="F78">
-        <v>0.04958760577823937</v>
+        <v>0.0364509107269253</v>
       </c>
       <c r="G78">
-        <v>1.094539831334923</v>
+        <v>0.8372702153735407</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="O78">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="79">
@@ -5289,22 +5289,22 @@
         </is>
       </c>
       <c r="B79">
-        <v>2.151055131270959</v>
+        <v>1.337435973381941</v>
       </c>
       <c r="C79">
-        <v>0.6916153335714653</v>
+        <v>0.7383674548310727</v>
       </c>
       <c r="D79">
-        <v>1.107492045516399</v>
+        <v>0.3937799890436393</v>
       </c>
       <c r="E79">
-        <v>0.2680812495407752</v>
+        <v>0.6937434796614685</v>
       </c>
       <c r="F79">
-        <v>0.5545586734867114</v>
+        <v>0.3146106958916202</v>
       </c>
       <c r="G79">
-        <v>8.343640445969868</v>
+        <v>5.685550447758135</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="O79">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="80">
@@ -5352,22 +5352,22 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.1940767474431474</v>
+        <v>0.1444728371834296</v>
       </c>
       <c r="C80">
-        <v>0.7670977089783362</v>
+        <v>0.8466159332230491</v>
       </c>
       <c r="D80">
-        <v>-2.137278698115936</v>
+        <v>-2.285172876092521</v>
       </c>
       <c r="E80">
-        <v>0.0325753303900712</v>
+        <v>0.02230269297329646</v>
       </c>
       <c r="F80">
-        <v>0.04315377089046747</v>
+        <v>0.02748814371468434</v>
       </c>
       <c r="G80">
-        <v>0.8728271741005944</v>
+        <v>0.7593237615634117</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="O80">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="81">
@@ -5415,22 +5415,22 @@
         </is>
       </c>
       <c r="B81">
-        <v>1.365465637298453</v>
+        <v>1.060202440509069</v>
       </c>
       <c r="C81">
-        <v>0.7474024686417439</v>
+        <v>0.7553648396722332</v>
       </c>
       <c r="D81">
-        <v>0.4167707624228954</v>
+        <v>0.07739289470635867</v>
       </c>
       <c r="E81">
-        <v>0.6768460899707651</v>
+        <v>0.9383109930337662</v>
       </c>
       <c r="F81">
-        <v>0.3155663166131219</v>
+        <v>0.2412243153156218</v>
       </c>
       <c r="G81">
-        <v>5.908413884770558</v>
+        <v>4.659684548759889</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="O81">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="82">
@@ -5478,22 +5478,22 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.2604555686296904</v>
+        <v>0.2147971885926073</v>
       </c>
       <c r="C82">
-        <v>0.6596812350331515</v>
+        <v>0.6704791449250075</v>
       </c>
       <c r="D82">
-        <v>-2.039353134170364</v>
+        <v>-2.293972924532807</v>
       </c>
       <c r="E82">
-        <v>0.04141479620624899</v>
+        <v>0.02179205401165507</v>
       </c>
       <c r="F82">
-        <v>0.07148451285575387</v>
+        <v>0.05771858955494173</v>
       </c>
       <c r="G82">
-        <v>0.9489762260407584</v>
+        <v>0.7993582757834019</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="O82">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="83">
@@ -5541,22 +5541,22 @@
         </is>
       </c>
       <c r="B83">
-        <v>2.125172781204648</v>
+        <v>1.362529649665635</v>
       </c>
       <c r="C83">
-        <v>0.5853034756701933</v>
+        <v>0.6160696972333136</v>
       </c>
       <c r="D83">
-        <v>1.287969641748663</v>
+        <v>0.5021233959894355</v>
       </c>
       <c r="E83">
-        <v>0.1977565311186125</v>
+        <v>0.6155807237860056</v>
       </c>
       <c r="F83">
-        <v>0.6748123515468468</v>
+        <v>0.4073300819773827</v>
       </c>
       <c r="G83">
-        <v>6.692763313564756</v>
+        <v>4.557696886038094</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="O83">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="84">
@@ -5604,22 +5604,22 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.2179584000617695</v>
+        <v>0.1824378189024235</v>
       </c>
       <c r="C84">
-        <v>0.6524191469469002</v>
+        <v>0.7071770260135042</v>
       </c>
       <c r="D84">
-        <v>-2.3350802424124</v>
+        <v>-2.405827423369477</v>
       </c>
       <c r="E84">
-        <v>0.01953922925398197</v>
+        <v>0.01613588519610834</v>
       </c>
       <c r="F84">
-        <v>0.0606783030380064</v>
+        <v>0.04562098896496276</v>
       </c>
       <c r="G84">
-        <v>0.782913525576525</v>
+        <v>0.7295667744387454</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="O84">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="85">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.435441762442814</v>
+        <v>1.115951587098342</v>
       </c>
       <c r="C85">
-        <v>0.6277978702550312</v>
+        <v>0.6448539034618052</v>
       </c>
       <c r="D85">
-        <v>0.575778713746439</v>
+        <v>0.1701276547958322</v>
       </c>
       <c r="E85">
-        <v>0.5647647631086308</v>
+        <v>0.8649097451534535</v>
       </c>
       <c r="F85">
-        <v>0.4193755058561236</v>
+        <v>0.3153150618112398</v>
       </c>
       <c r="G85">
-        <v>4.913241294716508</v>
+        <v>3.949535228649568</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.8669775724812994</v>
+        <v>0.8782453093204918</v>
       </c>
       <c r="C86">
-        <v>0.05741438310691479</v>
+        <v>0.06354665151897385</v>
       </c>
       <c r="D86">
-        <v>-2.486174417782154</v>
+        <v>-2.04305538822147</v>
       </c>
       <c r="E86">
-        <v>0.0129124662621191</v>
+        <v>0.0410469554363754</v>
       </c>
       <c r="F86">
-        <v>0.7747055219007641</v>
+        <v>0.775398276009139</v>
       </c>
       <c r="G86">
-        <v>0.9702397749035913</v>
+        <v>0.9947337351757995</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.095680840112689</v>
+        <v>1.059291771978801</v>
       </c>
       <c r="C87">
-        <v>0.05973530231927247</v>
+        <v>0.05909716078304806</v>
       </c>
       <c r="D87">
-        <v>1.529680746445312</v>
+        <v>0.9746753382625362</v>
       </c>
       <c r="E87">
-        <v>0.1260957716505511</v>
+        <v>0.3297213298295043</v>
       </c>
       <c r="F87">
-        <v>0.9746244133167323</v>
+        <v>0.9434350447393713</v>
       </c>
       <c r="G87">
-        <v>1.231773478056623</v>
+        <v>1.189376061912109</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.8543038711382949</v>
+        <v>0.8675879750322819</v>
       </c>
       <c r="C88">
-        <v>0.06598542245843241</v>
+        <v>0.06465846608787464</v>
       </c>
       <c r="D88">
-        <v>-2.386410840621904</v>
+        <v>-2.196748063416613</v>
       </c>
       <c r="E88">
-        <v>0.01701373230085127</v>
+        <v>0.02803844416593843</v>
       </c>
       <c r="F88">
-        <v>0.750663813680592</v>
+        <v>0.7643216083989577</v>
       </c>
       <c r="G88">
-        <v>0.9722529459138439</v>
+        <v>0.9848065083457896</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.039157088776906</v>
+        <v>1.024042733226725</v>
       </c>
       <c r="C89">
-        <v>0.054711642654996</v>
+        <v>0.06272273757294054</v>
       </c>
       <c r="D89">
-        <v>0.7020424009010157</v>
+        <v>0.3787822141160437</v>
       </c>
       <c r="E89">
-        <v>0.4826527212434492</v>
+        <v>0.7048495960309553</v>
       </c>
       <c r="F89">
-        <v>0.9334919344345565</v>
+        <v>0.9055832667420469</v>
       </c>
       <c r="G89">
-        <v>1.156782844416745</v>
+        <v>1.157997898136043</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="O89">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="90">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.2656744807609598</v>
+        <v>0.2457417039743205</v>
       </c>
       <c r="C90">
-        <v>0.6133201035173811</v>
+        <v>0.6548661824009021</v>
       </c>
       <c r="D90">
-        <v>-2.161160980274477</v>
+        <v>-2.143146670618587</v>
       </c>
       <c r="E90">
-        <v>0.03068290639245883</v>
+        <v>0.03210132292510331</v>
       </c>
       <c r="F90">
-        <v>0.07985292370482075</v>
+        <v>0.06808567701973084</v>
       </c>
       <c r="G90">
-        <v>0.8839116522335235</v>
+        <v>0.8869557844699434</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="O90">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="91">
@@ -6045,22 +6045,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>2.252750600939793</v>
+        <v>1.718632937506967</v>
       </c>
       <c r="C91">
-        <v>0.5928988713879891</v>
+        <v>0.6068530432502138</v>
       </c>
       <c r="D91">
-        <v>1.369798456505783</v>
+        <v>0.8923563571931858</v>
       </c>
       <c r="E91">
-        <v>0.1707498240244409</v>
+        <v>0.3722019557247372</v>
       </c>
       <c r="F91">
-        <v>0.7047525888928153</v>
+        <v>0.5231531972422997</v>
       </c>
       <c r="G91">
-        <v>7.200945906431325</v>
+        <v>5.645954549171594</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="O91">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="92">
@@ -6108,22 +6108,22 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.2105920614352351</v>
+        <v>0.1972043662289036</v>
       </c>
       <c r="C92">
-        <v>0.6627019919917218</v>
+        <v>0.688115192349302</v>
       </c>
       <c r="D92">
-        <v>-2.350728372341429</v>
+        <v>-2.359364702290109</v>
       </c>
       <c r="E92">
-        <v>0.01873670598769872</v>
+        <v>0.01830625491010182</v>
       </c>
       <c r="F92">
-        <v>0.05745780585492033</v>
+        <v>0.05119078773593552</v>
       </c>
       <c r="G92">
-        <v>0.7718536355447008</v>
+        <v>0.759698449266945</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O92">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="93">
@@ -6171,22 +6171,22 @@
         </is>
       </c>
       <c r="B93">
-        <v>1.378020919992705</v>
+        <v>1.285972224809249</v>
       </c>
       <c r="C93">
-        <v>0.5858205151365347</v>
+        <v>0.6266162444729609</v>
       </c>
       <c r="D93">
-        <v>0.5473491378473754</v>
+        <v>0.401386063119342</v>
       </c>
       <c r="E93">
-        <v>0.5841388913006054</v>
+        <v>0.6881359087389085</v>
       </c>
       <c r="F93">
-        <v>0.4371238313127193</v>
+        <v>0.3765779390114435</v>
       </c>
       <c r="G93">
-        <v>4.344173252313563</v>
+        <v>4.39145364521897</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="O93">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="94">
@@ -6234,22 +6234,22 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.3630243452619096</v>
+        <v>0.3738211199679969</v>
       </c>
       <c r="C94">
-        <v>0.3781483032905013</v>
+        <v>0.4091055291757064</v>
       </c>
       <c r="D94">
-        <v>-2.679597849075956</v>
+        <v>-2.405193317290072</v>
       </c>
       <c r="E94">
-        <v>0.007371065642614525</v>
+        <v>0.01616391266089837</v>
       </c>
       <c r="F94">
-        <v>0.1730036761318169</v>
+        <v>0.1676612024403737</v>
       </c>
       <c r="G94">
-        <v>0.7617565025174711</v>
+        <v>0.8334798253867041</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="O94">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="95">
@@ -6297,22 +6297,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.638717607831907</v>
+        <v>1.393840405247607</v>
       </c>
       <c r="C95">
-        <v>0.3697708088809238</v>
+        <v>0.3728864602691571</v>
       </c>
       <c r="D95">
-        <v>1.335730072926379</v>
+        <v>0.8905199149216135</v>
       </c>
       <c r="E95">
-        <v>0.1816375161636782</v>
+        <v>0.3731867798518935</v>
       </c>
       <c r="F95">
-        <v>0.7938795905404494</v>
+        <v>0.6711375210701196</v>
       </c>
       <c r="G95">
-        <v>3.3826230453792</v>
+        <v>2.894773447032228</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="O95">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="96">
@@ -6360,22 +6360,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.3321555642798949</v>
+        <v>0.3348898977341579</v>
       </c>
       <c r="C96">
-        <v>0.4206505382712737</v>
+        <v>0.4244320661618659</v>
       </c>
       <c r="D96">
-        <v>-2.620112783476461</v>
+        <v>-2.577452440272675</v>
       </c>
       <c r="E96">
-        <v>0.008790069088255576</v>
+        <v>0.009953157730940311</v>
       </c>
       <c r="F96">
-        <v>0.1456408298423358</v>
+        <v>0.1457554548732887</v>
       </c>
       <c r="G96">
-        <v>0.757530144544842</v>
+        <v>0.7694480024908332</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="O96">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="97">
@@ -6423,22 +6423,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>1.14061673531121</v>
+        <v>1.132863571125341</v>
       </c>
       <c r="C97">
-        <v>0.3584860188099636</v>
+        <v>0.3990596194722572</v>
       </c>
       <c r="D97">
-        <v>0.3670132309334461</v>
+        <v>0.3126063246536109</v>
       </c>
       <c r="E97">
-        <v>0.7136091487998394</v>
+        <v>0.7545797724218383</v>
       </c>
       <c r="F97">
-        <v>0.564931624456129</v>
+        <v>0.5182000466199354</v>
       </c>
       <c r="G97">
-        <v>2.302945136280001</v>
+        <v>2.476610874803978</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.9434878302604727</v>
+        <v>0.7980613194882404</v>
       </c>
       <c r="C98">
-        <v>0.2211726086814911</v>
+        <v>0.2297834998149982</v>
       </c>
       <c r="D98">
-        <v>-0.2630154480184967</v>
+        <v>-0.98166249187662</v>
       </c>
       <c r="E98">
-        <v>0.7925386723959743</v>
+        <v>0.3262661496323542</v>
       </c>
       <c r="F98">
-        <v>0.6116089568148401</v>
+        <v>0.508679449064305</v>
       </c>
       <c r="G98">
-        <v>1.455454953579279</v>
+        <v>1.252069197674225</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.184112389641913</v>
+        <v>1.060090448187963</v>
       </c>
       <c r="C99">
-        <v>0.1650571449105133</v>
+        <v>0.1952095735899113</v>
       </c>
       <c r="D99">
-        <v>1.023848169265953</v>
+        <v>0.2989312044987458</v>
       </c>
       <c r="E99">
-        <v>0.305906994552682</v>
+        <v>0.7649925373441253</v>
       </c>
       <c r="F99">
-        <v>0.8568326927478077</v>
+        <v>0.7230698134398443</v>
       </c>
       <c r="G99">
-        <v>1.636401322184574</v>
+        <v>1.554195372910351</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.9334254359670295</v>
+        <v>0.8875095840599678</v>
       </c>
       <c r="C100">
-        <v>0.1999371136271721</v>
+        <v>0.2492114882150324</v>
       </c>
       <c r="D100">
-        <v>-0.3445793215303823</v>
+        <v>-0.4788541636053968</v>
       </c>
       <c r="E100">
-        <v>0.7304106537680126</v>
+        <v>0.63204238117718</v>
       </c>
       <c r="F100">
-        <v>0.6308016949926036</v>
+        <v>0.5445576309825237</v>
       </c>
       <c r="G100">
-        <v>1.381231298879841</v>
+        <v>1.446446100437762</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>1.383113373556149</v>
+        <v>1.163553538936954</v>
       </c>
       <c r="C101">
-        <v>0.2015349763256648</v>
+        <v>0.2095147366038292</v>
       </c>
       <c r="D101">
-        <v>1.609333683794846</v>
+        <v>0.722997916868919</v>
       </c>
       <c r="E101">
-        <v>0.1075433975163497</v>
+        <v>0.4696811640193486</v>
       </c>
       <c r="F101">
-        <v>0.9317746649257762</v>
+        <v>0.7716975194998055</v>
       </c>
       <c r="G101">
-        <v>2.053074285146247</v>
+        <v>1.754387961296344</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="O101">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="102">
@@ -6738,22 +6738,22 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.4456077050108032</v>
+        <v>0.1924031638845731</v>
       </c>
       <c r="C102">
-        <v>1.4423809771423</v>
+        <v>1.508401883488374</v>
       </c>
       <c r="D102">
-        <v>-0.5604041595190334</v>
+        <v>-1.092654626476358</v>
       </c>
       <c r="E102">
-        <v>0.5752037950959357</v>
+        <v>0.2745454685773949</v>
       </c>
       <c r="F102">
-        <v>0.02637520099935631</v>
+        <v>0.01000594700323432</v>
       </c>
       <c r="G102">
-        <v>7.528519944543397</v>
+        <v>3.699697535958155</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="O102">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="103">
@@ -6801,22 +6801,22 @@
         </is>
       </c>
       <c r="B103">
-        <v>2.337087488941431</v>
+        <v>1.888851132325813</v>
       </c>
       <c r="C103">
-        <v>1.076654950470963</v>
+        <v>1.310648349768326</v>
       </c>
       <c r="D103">
-        <v>0.7884656926683816</v>
+        <v>0.4852321966177636</v>
       </c>
       <c r="E103">
-        <v>0.4304243583250354</v>
+        <v>0.6275116457284027</v>
       </c>
       <c r="F103">
-        <v>0.2832856757888151</v>
+        <v>0.144734422602643</v>
       </c>
       <c r="G103">
-        <v>19.28081226047723</v>
+        <v>24.6503805793561</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="O103">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="104">
@@ -6864,22 +6864,22 @@
         </is>
       </c>
       <c r="B104">
-        <v>0.482826353677188</v>
+        <v>0.400729010089964</v>
       </c>
       <c r="C104">
-        <v>1.301626521200468</v>
+        <v>1.61756015638744</v>
       </c>
       <c r="D104">
-        <v>-0.5593756690634969</v>
+        <v>-0.5653390149492303</v>
       </c>
       <c r="E104">
-        <v>0.5759053629963951</v>
+        <v>0.5718431964721644</v>
       </c>
       <c r="F104">
-        <v>0.03765689117145059</v>
+        <v>0.01682600765707618</v>
       </c>
       <c r="G104">
-        <v>6.190667379944229</v>
+        <v>9.543781436480508</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="O104">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="105">
@@ -6927,22 +6927,22 @@
         </is>
       </c>
       <c r="B105">
-        <v>4.806843600163342</v>
+        <v>3.39215249607704</v>
       </c>
       <c r="C105">
-        <v>1.295483831747514</v>
+        <v>1.371157135418231</v>
       </c>
       <c r="D105">
-        <v>1.211933807320051</v>
+        <v>0.8908276396172534</v>
       </c>
       <c r="E105">
-        <v>0.2255377196832544</v>
+        <v>0.3730216446909655</v>
       </c>
       <c r="F105">
-        <v>0.3794391641572349</v>
+        <v>0.2308576647981559</v>
       </c>
       <c r="G105">
-        <v>60.89446630463414</v>
+        <v>49.84325977091669</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="O105">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="106">
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.5224777081059661</v>
+        <v>0.2289994834722243</v>
       </c>
       <c r="C106">
-        <v>1.270487301862173</v>
+        <v>1.319458821851675</v>
       </c>
       <c r="D106">
-        <v>-0.5109637530527263</v>
+        <v>-1.117151597760093</v>
       </c>
       <c r="E106">
-        <v>0.60937643807029</v>
+        <v>0.2639295119305226</v>
       </c>
       <c r="F106">
-        <v>0.04331387249097927</v>
+        <v>0.01724682343904771</v>
       </c>
       <c r="G106">
-        <v>6.302437066196648</v>
+        <v>3.040604179423378</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="O106">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="107">
@@ -7053,22 +7053,22 @@
         </is>
       </c>
       <c r="B107">
-        <v>2.401812014058314</v>
+        <v>1.617559017528944</v>
       </c>
       <c r="C107">
-        <v>0.9306055994675225</v>
+        <v>1.133917931396458</v>
       </c>
       <c r="D107">
-        <v>0.9415626328052911</v>
+        <v>0.4241208471016576</v>
       </c>
       <c r="E107">
-        <v>0.3464166084800374</v>
+        <v>0.6714776825706842</v>
       </c>
       <c r="F107">
-        <v>0.3876199225844916</v>
+        <v>0.1752537994110364</v>
       </c>
       <c r="G107">
-        <v>14.88236443682128</v>
+        <v>14.92976006216293</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O107">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="108">
@@ -7116,22 +7116,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.5254479229892746</v>
+        <v>0.4447357633127028</v>
       </c>
       <c r="C108">
-        <v>1.138072671531985</v>
+        <v>1.426963410871557</v>
       </c>
       <c r="D108">
-        <v>-0.5654333063238225</v>
+        <v>-0.5678316327626203</v>
       </c>
       <c r="E108">
-        <v>0.571779075748774</v>
+        <v>0.570149298279115</v>
       </c>
       <c r="F108">
-        <v>0.05646774767144776</v>
+        <v>0.02713117465293285</v>
       </c>
       <c r="G108">
-        <v>4.889437442771372</v>
+        <v>7.290134013712949</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O108">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="109">
@@ -7179,22 +7179,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>5.493161573601435</v>
+        <v>2.885110812241928</v>
       </c>
       <c r="C109">
-        <v>1.134656506547095</v>
+        <v>1.207794301393623</v>
       </c>
       <c r="D109">
-        <v>1.501338914952235</v>
+        <v>0.8772713265736307</v>
       </c>
       <c r="E109">
-        <v>0.1332679245952953</v>
+        <v>0.3803392825305528</v>
       </c>
       <c r="F109">
-        <v>0.5942935324680303</v>
+        <v>0.2704494640260046</v>
       </c>
       <c r="G109">
-        <v>50.77427638894026</v>
+        <v>30.77789201355159</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.8463856535394402</v>
+        <v>0.8517818695642642</v>
       </c>
       <c r="C110">
-        <v>0.07627666960764061</v>
+        <v>0.0868771993969495</v>
       </c>
       <c r="D110">
-        <v>-2.186516124218409</v>
+        <v>-1.8465697292698</v>
       </c>
       <c r="E110">
-        <v>0.02877786632964121</v>
+        <v>0.06480952474321205</v>
       </c>
       <c r="F110">
-        <v>0.7288555656449881</v>
+        <v>0.7184199527797931</v>
       </c>
       <c r="G110">
-        <v>0.9828678112424748</v>
+        <v>1.009900059862035</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.075191986173269</v>
+        <v>1.047288767390359</v>
       </c>
       <c r="C111">
-        <v>0.07826952115361897</v>
+        <v>0.07950273651660282</v>
       </c>
       <c r="D111">
-        <v>0.9262767467403349</v>
+        <v>0.5811711704663097</v>
       </c>
       <c r="E111">
-        <v>0.3543021771075274</v>
+        <v>0.5611250957767475</v>
       </c>
       <c r="F111">
-        <v>0.9222801925430631</v>
+        <v>0.8961765869211377</v>
       </c>
       <c r="G111">
-        <v>1.25345618010466</v>
+        <v>1.223881295616279</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.8877760231426421</v>
+        <v>0.9170016358587306</v>
       </c>
       <c r="C112">
-        <v>0.08255610891684907</v>
+        <v>0.08263016030663047</v>
       </c>
       <c r="D112">
-        <v>-1.441877476504545</v>
+        <v>-1.048600444211529</v>
       </c>
       <c r="E112">
-        <v>0.1493369412454314</v>
+        <v>0.2943620513317699</v>
       </c>
       <c r="F112">
-        <v>0.7551470396621931</v>
+        <v>0.7798933019395923</v>
       </c>
       <c r="G112">
-        <v>1.043699075639009</v>
+        <v>1.078214158367936</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>1.066322680500718</v>
+        <v>1.045185603299807</v>
       </c>
       <c r="C113">
-        <v>0.07049446715581754</v>
+        <v>0.08326618303542691</v>
       </c>
       <c r="D113">
-        <v>0.9109364846312025</v>
+        <v>0.5307614549864771</v>
       </c>
       <c r="E113">
-        <v>0.3623288406405746</v>
+        <v>0.5955840936277297</v>
       </c>
       <c r="F113">
-        <v>0.9287175391873267</v>
+        <v>0.8878040369793347</v>
       </c>
       <c r="G113">
-        <v>1.224316340515337</v>
+        <v>1.230466296438579</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="O113">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="114">
@@ -7494,22 +7494,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.2605848690163686</v>
+        <v>0.1914224563859067</v>
       </c>
       <c r="C114">
-        <v>0.8469227303143787</v>
+        <v>0.9424125599543023</v>
       </c>
       <c r="D114">
-        <v>-1.58789772660758</v>
+        <v>-1.754298011409796</v>
       </c>
       <c r="E114">
-        <v>0.1123094676641741</v>
+        <v>0.07937945635380822</v>
       </c>
       <c r="F114">
-        <v>0.04955041082189979</v>
+        <v>0.03018629830860673</v>
       </c>
       <c r="G114">
-        <v>1.370411926640702</v>
+        <v>1.213880431254031</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="O114">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="115">
@@ -7557,22 +7557,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>1.996131862673465</v>
+        <v>1.907249376651286</v>
       </c>
       <c r="C115">
-        <v>0.8282721840051687</v>
+        <v>0.864509143634129</v>
       </c>
       <c r="D115">
-        <v>0.8345218546739512</v>
+        <v>0.7468539713100467</v>
       </c>
       <c r="E115">
-        <v>0.4039869772684682</v>
+        <v>0.4551517127641684</v>
       </c>
       <c r="F115">
-        <v>0.3936975079486272</v>
+        <v>0.3503773022606272</v>
       </c>
       <c r="G115">
-        <v>10.12082203400732</v>
+        <v>10.38195157410882</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="O115">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="116">
@@ -7620,22 +7620,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.2726892228491024</v>
+        <v>0.2862317110407399</v>
       </c>
       <c r="C116">
-        <v>0.9177349754253142</v>
+        <v>0.9474384107083345</v>
       </c>
       <c r="D116">
-        <v>-1.415901698070632</v>
+        <v>-1.320353495886158</v>
       </c>
       <c r="E116">
-        <v>0.1568042877203713</v>
+        <v>0.1867170224057649</v>
       </c>
       <c r="F116">
-        <v>0.04513262013762068</v>
+        <v>0.04469477027582344</v>
       </c>
       <c r="G116">
-        <v>1.647575789557685</v>
+        <v>1.833068878074688</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="O116">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="117">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>2.192151048913623</v>
+        <v>2.367357870246097</v>
       </c>
       <c r="C117">
-        <v>0.8088274927416631</v>
+        <v>0.8836585226026962</v>
       </c>
       <c r="D117">
-        <v>0.9703963860415572</v>
+        <v>0.9752347638212008</v>
       </c>
       <c r="E117">
-        <v>0.3318489493864824</v>
+        <v>0.3294438216412195</v>
       </c>
       <c r="F117">
-        <v>0.449153993731545</v>
+        <v>0.4188826925343073</v>
       </c>
       <c r="G117">
-        <v>10.69906154307806</v>
+        <v>13.37936225511902</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="O117">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="118">
@@ -7746,22 +7746,22 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.2937361338526142</v>
+        <v>0.2774649018733938</v>
       </c>
       <c r="C118">
-        <v>0.52011697093255</v>
+        <v>0.5847659782925985</v>
       </c>
       <c r="D118">
-        <v>-2.355380591306974</v>
+        <v>-2.192434035361919</v>
       </c>
       <c r="E118">
-        <v>0.01850374299225487</v>
+        <v>0.02834818130514232</v>
       </c>
       <c r="F118">
-        <v>0.1059822184599291</v>
+        <v>0.08819710934539285</v>
       </c>
       <c r="G118">
-        <v>0.8141074756167981</v>
+        <v>0.8728945012258913</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="O118">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="119">
@@ -7809,22 +7809,22 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.492435017656819</v>
+        <v>1.384429916102129</v>
       </c>
       <c r="C119">
-        <v>0.5053961053665837</v>
+        <v>0.5250683772732839</v>
       </c>
       <c r="D119">
-        <v>0.792267731837612</v>
+        <v>0.6195163450330868</v>
       </c>
       <c r="E119">
-        <v>0.4282045825297723</v>
+        <v>0.5355762575877469</v>
       </c>
       <c r="F119">
-        <v>0.5542446194329331</v>
+        <v>0.4946886684587355</v>
       </c>
       <c r="G119">
-        <v>4.018735056385752</v>
+        <v>3.874449355329074</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="O119">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="120">
@@ -7872,22 +7872,22 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.4007586528392432</v>
+        <v>0.437592392284616</v>
       </c>
       <c r="C120">
-        <v>0.5510632261347839</v>
+        <v>0.565471090707785</v>
       </c>
       <c r="D120">
-        <v>-1.659330277807518</v>
+        <v>-1.461555553761415</v>
       </c>
       <c r="E120">
-        <v>0.09704925728972269</v>
+        <v>0.1438630415769355</v>
       </c>
       <c r="F120">
-        <v>0.1360871251113627</v>
+        <v>0.1444574345804798</v>
       </c>
       <c r="G120">
-        <v>1.180181429316674</v>
+        <v>1.325560725493103</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="O120">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="121">
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="B121">
-        <v>1.409897178476787</v>
+        <v>1.458385258394906</v>
       </c>
       <c r="C121">
-        <v>0.4805564015666111</v>
+        <v>0.5557151203158767</v>
       </c>
       <c r="D121">
-        <v>0.714831344552043</v>
+        <v>0.6789986856028419</v>
       </c>
       <c r="E121">
-        <v>0.4747132643482031</v>
+        <v>0.4971386947726804</v>
       </c>
       <c r="F121">
-        <v>0.5497143710882633</v>
+        <v>0.4907346204334925</v>
       </c>
       <c r="G121">
-        <v>3.616078018738274</v>
+        <v>4.334089084696699</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7725</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.098878830610882</v>
+        <v>1.000494522046807</v>
       </c>
       <c r="C122">
-        <v>0.1014650524343165</v>
+        <v>0.1024484140062921</v>
       </c>
       <c r="D122">
-        <v>0.9292895717258168</v>
+        <v>0.004825841530806892</v>
       </c>
       <c r="E122">
-        <v>0.3527390381194196</v>
+        <v>0.9961495504950508</v>
       </c>
       <c r="F122">
-        <v>0.9007050501071366</v>
+        <v>0.8184845143363915</v>
       </c>
       <c r="G122">
-        <v>1.340654950498064</v>
+        <v>1.222978897111142</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.9376305868373739</v>
+        <v>0.9508501671415989</v>
       </c>
       <c r="C123">
-        <v>0.06226000600023247</v>
+        <v>0.05738715202111361</v>
       </c>
       <c r="D123">
-        <v>-1.034359653147411</v>
+        <v>-0.8782241325388964</v>
       </c>
       <c r="E123">
-        <v>0.3009680589067848</v>
+        <v>0.3798220981848224</v>
       </c>
       <c r="F123">
-        <v>0.8299194694572009</v>
+        <v>0.8496969411138124</v>
       </c>
       <c r="G123">
-        <v>1.059320994057407</v>
+        <v>1.064045304397659</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.082173261387748</v>
+        <v>0.9640053325556573</v>
       </c>
       <c r="C124">
-        <v>0.1041865704729233</v>
+        <v>0.1062496394320345</v>
       </c>
       <c r="D124">
-        <v>0.7579796313370468</v>
+        <v>-0.3450219020611435</v>
       </c>
       <c r="E124">
-        <v>0.448463176585847</v>
+        <v>0.7300779051355285</v>
       </c>
       <c r="F124">
-        <v>0.8822933979782666</v>
+        <v>0.7827797446176503</v>
       </c>
       <c r="G124">
-        <v>1.327335068296004</v>
+        <v>1.187187440126807</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="O124">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="125">
@@ -8187,22 +8187,22 @@
         </is>
       </c>
       <c r="B125">
-        <v>2.488437887530892</v>
+        <v>1.503183655307805</v>
       </c>
       <c r="C125">
-        <v>0.6966328864289227</v>
+        <v>0.7470449871527196</v>
       </c>
       <c r="D125">
-        <v>1.308659377072419</v>
+        <v>0.5455967214856857</v>
       </c>
       <c r="E125">
-        <v>0.1906497579823719</v>
+        <v>0.5853431784803502</v>
       </c>
       <c r="F125">
-        <v>0.6352604487651057</v>
+        <v>0.3476371645050937</v>
       </c>
       <c r="G125">
-        <v>9.747691883126954</v>
+        <v>6.499768529643001</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="O125">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="126">
@@ -8250,22 +8250,22 @@
         </is>
       </c>
       <c r="B126">
-        <v>0.6509864451685373</v>
+        <v>0.7609362092114333</v>
       </c>
       <c r="C126">
-        <v>0.3833296190035641</v>
+        <v>0.3636889723037983</v>
       </c>
       <c r="D126">
-        <v>-1.119836394745312</v>
+        <v>-0.7512071313448234</v>
       </c>
       <c r="E126">
-        <v>0.2627834869371209</v>
+        <v>0.4525280090694187</v>
       </c>
       <c r="F126">
-        <v>0.3071009659958918</v>
+        <v>0.3730573801915464</v>
       </c>
       <c r="G126">
-        <v>1.379947960824188</v>
+        <v>1.552104167438709</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="O126">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="127">
@@ -8313,22 +8313,22 @@
         </is>
       </c>
       <c r="B127">
-        <v>2.206591385134572</v>
+        <v>1.185955875647173</v>
       </c>
       <c r="C127">
-        <v>0.705596433742418</v>
+        <v>0.7550120863847439</v>
       </c>
       <c r="D127">
-        <v>1.121673703767408</v>
+        <v>0.2258892256352766</v>
       </c>
       <c r="E127">
-        <v>0.2620012012244486</v>
+        <v>0.8212875779596518</v>
       </c>
       <c r="F127">
-        <v>0.5534993879839512</v>
+        <v>0.2700231989418979</v>
       </c>
       <c r="G127">
-        <v>8.79683997246134</v>
+        <v>5.208779632614806</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O127">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="128">
@@ -8376,22 +8376,22 @@
         </is>
       </c>
       <c r="B128">
-        <v>2.163014629080444</v>
+        <v>1.319286750240557</v>
       </c>
       <c r="C128">
-        <v>0.5923548430011977</v>
+        <v>0.6244851302181866</v>
       </c>
       <c r="D128">
-        <v>1.302433700665137</v>
+        <v>0.4437115255858177</v>
       </c>
       <c r="E128">
-        <v>0.1927681683878262</v>
+        <v>0.6572511614945908</v>
       </c>
       <c r="F128">
-        <v>0.677401416123255</v>
+        <v>0.3879506592705687</v>
       </c>
       <c r="G128">
-        <v>6.906735318611617</v>
+        <v>4.486440447434322</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="O128">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="129">
@@ -8439,22 +8439,22 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.6550246667744777</v>
+        <v>0.7495408841084947</v>
       </c>
       <c r="C129">
-        <v>0.3541867296109809</v>
+        <v>0.3385361542810397</v>
       </c>
       <c r="D129">
-        <v>-1.194517889823228</v>
+        <v>-0.8515912134381265</v>
       </c>
       <c r="E129">
-        <v>0.2322754469769736</v>
+        <v>0.3944410180455482</v>
       </c>
       <c r="F129">
-        <v>0.3271699171608203</v>
+        <v>0.3860404646653559</v>
       </c>
       <c r="G129">
-        <v>1.31142043194672</v>
+        <v>1.455317740945</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="O129">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="130">
@@ -8502,22 +8502,22 @@
         </is>
       </c>
       <c r="B130">
-        <v>2.002892866057798</v>
+        <v>1.082428401318102</v>
       </c>
       <c r="C130">
-        <v>0.6071532490053621</v>
+        <v>0.6438509975535869</v>
       </c>
       <c r="D130">
-        <v>1.144015237751105</v>
+        <v>0.1230207564150241</v>
       </c>
       <c r="E130">
-        <v>0.2526173177027087</v>
+        <v>0.9020906615697579</v>
       </c>
       <c r="F130">
-        <v>0.6093235127879848</v>
+        <v>0.3064447717541008</v>
       </c>
       <c r="G130">
-        <v>6.583661632471844</v>
+        <v>3.823368358590318</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9855669322288227</v>
+        <v>0.969497926654368</v>
       </c>
       <c r="C131">
-        <v>0.04471365883181319</v>
+        <v>0.04280847181170008</v>
       </c>
       <c r="D131">
-        <v>-0.325140864106155</v>
+        <v>-0.7236171150900876</v>
       </c>
       <c r="E131">
-        <v>0.7450744625913766</v>
+        <v>0.4693008310105575</v>
       </c>
       <c r="F131">
-        <v>0.9028711754420939</v>
+        <v>0.8914731090400079</v>
       </c>
       <c r="G131">
-        <v>1.075836956947166</v>
+        <v>1.054351746851105</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.9747152988139557</v>
+        <v>0.9667676352576254</v>
       </c>
       <c r="C132">
-        <v>0.03773191923136764</v>
+        <v>0.03513682315370398</v>
       </c>
       <c r="D132">
-        <v>-0.6787317571726263</v>
+        <v>-0.9618714451183628</v>
       </c>
       <c r="E132">
-        <v>0.497307840430142</v>
+        <v>0.3361141839111098</v>
       </c>
       <c r="F132">
-        <v>0.9052328689702367</v>
+        <v>0.9024301257391446</v>
       </c>
       <c r="G132">
-        <v>1.049530950884215</v>
+        <v>1.035691998664268</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.9643235523613513</v>
+        <v>0.9354892669566901</v>
       </c>
       <c r="C133">
-        <v>0.04764012714051921</v>
+        <v>0.04677704918693521</v>
       </c>
       <c r="D133">
-        <v>-0.762558952618314</v>
+        <v>-1.425605239071301</v>
       </c>
       <c r="E133">
-        <v>0.4457264723144924</v>
+        <v>0.1539823231328808</v>
       </c>
       <c r="F133">
-        <v>0.8783577230611904</v>
+        <v>0.8535365294286205</v>
       </c>
       <c r="G133">
-        <v>1.058702951228031</v>
+        <v>1.025310737640025</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="O133">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="134">
@@ -8754,22 +8754,22 @@
         </is>
       </c>
       <c r="B134">
-        <v>1.534251094532088</v>
+        <v>1.080171046619103</v>
       </c>
       <c r="C134">
-        <v>0.5751279287049942</v>
+        <v>0.5787359330659391</v>
       </c>
       <c r="D134">
-        <v>0.7442559373693028</v>
+        <v>0.1332549107267507</v>
       </c>
       <c r="E134">
-        <v>0.456721652776332</v>
+        <v>0.8939917855314247</v>
       </c>
       <c r="F134">
-        <v>0.4969888682223483</v>
+        <v>0.347433437087925</v>
       </c>
       <c r="G134">
-        <v>4.736376550027241</v>
+        <v>3.35825330956541</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="O134">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="135">
@@ -8817,22 +8817,22 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.6801951395748554</v>
+        <v>0.7004299248349332</v>
       </c>
       <c r="C135">
-        <v>0.3631917731742531</v>
+        <v>0.3407875492675445</v>
       </c>
       <c r="D135">
-        <v>-1.061080069762675</v>
+        <v>-1.044817966204223</v>
       </c>
       <c r="E135">
-        <v>0.2886535144482205</v>
+        <v>0.296107109652203</v>
       </c>
       <c r="F135">
-        <v>0.3337983045789152</v>
+        <v>0.3591582150697564</v>
       </c>
       <c r="G135">
-        <v>1.38606284560045</v>
+        <v>1.365977608249847</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="O135">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="136">
@@ -8880,22 +8880,22 @@
         </is>
       </c>
       <c r="B136">
-        <v>1.274534538727895</v>
+        <v>0.8116670585297627</v>
       </c>
       <c r="C136">
-        <v>0.5889543889567429</v>
+        <v>0.5937971466416979</v>
       </c>
       <c r="D136">
-        <v>0.4118842627563603</v>
+        <v>-0.3514079690776531</v>
       </c>
       <c r="E136">
-        <v>0.6804242560899316</v>
+        <v>0.7252823046984237</v>
       </c>
       <c r="F136">
-        <v>0.4018210870180672</v>
+        <v>0.2534760162486207</v>
       </c>
       <c r="G136">
-        <v>4.042690498065589</v>
+        <v>2.599075934885189</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="O136">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="137">
@@ -8943,22 +8943,22 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.9835262304776455</v>
+        <v>0.8482521552617573</v>
       </c>
       <c r="C137">
-        <v>0.3269289238278248</v>
+        <v>0.3225831785751342</v>
       </c>
       <c r="D137">
-        <v>-0.05080912013720219</v>
+        <v>-0.5101857301263415</v>
       </c>
       <c r="E137">
-        <v>0.9594776234471223</v>
+        <v>0.6099213484484725</v>
       </c>
       <c r="F137">
-        <v>0.5182073189426912</v>
+        <v>0.4507561619682308</v>
       </c>
       <c r="G137">
-        <v>1.86667345419053</v>
+        <v>1.596277055347119</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="O137">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="138">
@@ -9006,22 +9006,22 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.8014509712303106</v>
+        <v>0.7653753967712859</v>
       </c>
       <c r="C138">
-        <v>0.2485787132951504</v>
+        <v>0.2360391095347392</v>
       </c>
       <c r="D138">
-        <v>-0.8903879062514785</v>
+        <v>-1.132815876614898</v>
       </c>
       <c r="E138">
-        <v>0.373257633904693</v>
+        <v>0.2572915827396823</v>
       </c>
       <c r="F138">
-        <v>0.4923640951172865</v>
+        <v>0.4819007955799015</v>
       </c>
       <c r="G138">
-        <v>1.304570470624995</v>
+        <v>1.215601848670687</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="O138">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="139">
@@ -9069,22 +9069,22 @@
         </is>
       </c>
       <c r="B139">
-        <v>0.8574519417087464</v>
+        <v>0.6826839948501656</v>
       </c>
       <c r="C139">
-        <v>0.3443903997240738</v>
+        <v>0.3459802881416553</v>
       </c>
       <c r="D139">
-        <v>-0.4465575878141277</v>
+        <v>-1.103309095388135</v>
       </c>
       <c r="E139">
-        <v>0.6551945240214736</v>
+        <v>0.2698929581236661</v>
       </c>
       <c r="F139">
-        <v>0.4365803135467421</v>
+        <v>0.3465139841566408</v>
       </c>
       <c r="G139">
-        <v>1.684051730063598</v>
+        <v>1.344988826234213</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.198446581983926</v>
+        <v>1.131586912087261</v>
       </c>
       <c r="C140">
-        <v>0.1585808258390896</v>
+        <v>0.1843563148896822</v>
       </c>
       <c r="D140">
-        <v>1.141539036729948</v>
+        <v>0.6705547060057169</v>
       </c>
       <c r="E140">
-        <v>0.2536456768511541</v>
+        <v>0.5025042451009585</v>
       </c>
       <c r="F140">
-        <v>0.8782829206986134</v>
+        <v>0.7884307172366637</v>
       </c>
       <c r="G140">
-        <v>1.635320664924803</v>
+        <v>1.624098239215124</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.9718572377759541</v>
+        <v>1.090015690880763</v>
       </c>
       <c r="C141">
-        <v>0.1288355784109028</v>
+        <v>0.1355419701041564</v>
       </c>
       <c r="D141">
-        <v>-0.2215720251893258</v>
+        <v>0.6359070284625433</v>
       </c>
       <c r="E141">
-        <v>0.8246470618581083</v>
+        <v>0.5248370213464197</v>
       </c>
       <c r="F141">
-        <v>0.7549834476334852</v>
+        <v>0.835716959548554</v>
       </c>
       <c r="G141">
-        <v>1.251029401476399</v>
+        <v>1.42169450169838</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>1.42591105985406</v>
+        <v>1.261602119866316</v>
       </c>
       <c r="C142">
-        <v>0.164406251168195</v>
+        <v>0.1926536670047971</v>
       </c>
       <c r="D142">
-        <v>2.158135394226477</v>
+        <v>1.20621860241759</v>
       </c>
       <c r="E142">
-        <v>0.03091730660985283</v>
+        <v>0.2277332130537038</v>
       </c>
       <c r="F142">
-        <v>1.033117178201089</v>
+        <v>0.864839090538161</v>
       </c>
       <c r="G142">
-        <v>1.968046213455154</v>
+        <v>1.840388491066885</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="O142">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="143">
@@ -9321,22 +9321,22 @@
         </is>
       </c>
       <c r="B143">
-        <v>2.860954725982074</v>
+        <v>3.290641791245644</v>
       </c>
       <c r="C143">
-        <v>1.01373421440604</v>
+        <v>1.206535615306193</v>
       </c>
       <c r="D143">
-        <v>1.036914187626101</v>
+        <v>0.9871922585373702</v>
       </c>
       <c r="E143">
-        <v>0.2997758512542952</v>
+        <v>0.323548396189419</v>
       </c>
       <c r="F143">
-        <v>0.3923004962733128</v>
+        <v>0.3092257355654985</v>
       </c>
       <c r="G143">
-        <v>20.86426609671352</v>
+        <v>35.01753622960902</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="O143">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="144">
@@ -9384,22 +9384,22 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.850000082904492</v>
+        <v>1.809434464907629</v>
       </c>
       <c r="C144">
-        <v>0.827093566260113</v>
+        <v>0.8491542323565293</v>
       </c>
       <c r="D144">
-        <v>-0.1964938896791908</v>
+        <v>0.6983588181407054</v>
       </c>
       <c r="E144">
-        <v>0.844223614778758</v>
+        <v>0.4849528239273776</v>
       </c>
       <c r="F144">
-        <v>0.168033412793621</v>
+        <v>0.3425637981652968</v>
       </c>
       <c r="G144">
-        <v>4.299740920128901</v>
+        <v>9.557498779295212</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="O144">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="145">
@@ -9447,22 +9447,22 @@
         </is>
       </c>
       <c r="B145">
-        <v>7.431999746883474</v>
+        <v>6.377806955749759</v>
       </c>
       <c r="C145">
-        <v>1.020570361952811</v>
+        <v>1.230889042700221</v>
       </c>
       <c r="D145">
-        <v>1.96536666380933</v>
+        <v>1.505273210376142</v>
       </c>
       <c r="E145">
-        <v>0.04937181494341101</v>
+        <v>0.1322538497512808</v>
       </c>
       <c r="F145">
-        <v>1.005529043388823</v>
+        <v>0.5713953702218155</v>
       </c>
       <c r="G145">
-        <v>54.93090488120058</v>
+        <v>71.18787390422753</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="O145">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="146">
@@ -9510,22 +9510,22 @@
         </is>
       </c>
       <c r="B146">
-        <v>2.832093062418668</v>
+        <v>2.708005621317973</v>
       </c>
       <c r="C146">
-        <v>0.8731064495563784</v>
+        <v>1.037946557633142</v>
       </c>
       <c r="D146">
-        <v>1.192312846668397</v>
+        <v>0.9597916420076665</v>
       </c>
       <c r="E146">
-        <v>0.2331385991206086</v>
+        <v>0.3371600896406658</v>
       </c>
       <c r="F146">
-        <v>0.5115851892881864</v>
+        <v>0.3541178753812501</v>
       </c>
       <c r="G146">
-        <v>15.67823166530667</v>
+        <v>20.70862544624321</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O146">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="147">
@@ -9573,22 +9573,22 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.8211295109422466</v>
+        <v>1.696998100681006</v>
       </c>
       <c r="C147">
-        <v>0.7341326346367574</v>
+        <v>0.779612814569884</v>
       </c>
       <c r="D147">
-        <v>-0.2684452711600095</v>
+        <v>0.6783634865233381</v>
       </c>
       <c r="E147">
-        <v>0.7883565964693002</v>
+        <v>0.4975412543446439</v>
       </c>
       <c r="F147">
-        <v>0.194767652218455</v>
+        <v>0.3681914721339398</v>
       </c>
       <c r="G147">
-        <v>3.461836018765568</v>
+        <v>7.821480864356728</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="O147">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="148">
@@ -9636,22 +9636,22 @@
         </is>
       </c>
       <c r="B148">
-        <v>7.780269476837755</v>
+        <v>5.190537361283517</v>
       </c>
       <c r="C148">
-        <v>0.8972359943131974</v>
+        <v>1.076995023590092</v>
       </c>
       <c r="D148">
-        <v>2.286567845828059</v>
+        <v>1.529103843161748</v>
       </c>
       <c r="E148">
-        <v>0.02222105983097221</v>
+        <v>0.1262387027801724</v>
       </c>
       <c r="F148">
-        <v>1.340497401490717</v>
+        <v>0.6287420334361404</v>
       </c>
       <c r="G148">
-        <v>45.15681497397698</v>
+        <v>42.85013036529622</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.964535763713127</v>
+        <v>0.9482339513282371</v>
       </c>
       <c r="C149">
-        <v>0.06210946327712221</v>
+        <v>0.06029125313059968</v>
       </c>
       <c r="D149">
-        <v>-0.58136659638499</v>
+        <v>-0.8816208042093154</v>
       </c>
       <c r="E149">
-        <v>0.5609934054359083</v>
+        <v>0.3779819008825557</v>
       </c>
       <c r="F149">
-        <v>0.8539858295269666</v>
+        <v>0.8425496322649502</v>
       </c>
       <c r="G149">
-        <v>1.089396576986513</v>
+        <v>1.067174670807777</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.9670898990099857</v>
+        <v>1.001073232838127</v>
       </c>
       <c r="C150">
-        <v>0.07072548188397941</v>
+        <v>0.065918561603761</v>
       </c>
       <c r="D150">
-        <v>-0.4731508367324365</v>
+        <v>0.01627246270846883</v>
       </c>
       <c r="E150">
-        <v>0.6361055699425456</v>
+        <v>0.9870170262080562</v>
       </c>
       <c r="F150">
-        <v>0.8419091080812493</v>
+        <v>0.879743097033411</v>
       </c>
       <c r="G150">
-        <v>1.110883424101032</v>
+        <v>1.139136664879018</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>1.007187200225686</v>
+        <v>0.952368030063643</v>
       </c>
       <c r="C151">
-        <v>0.06512037376677422</v>
+        <v>0.06816674748384474</v>
       </c>
       <c r="D151">
-        <v>0.1099731923861875</v>
+        <v>-0.7159463300816163</v>
       </c>
       <c r="E151">
-        <v>0.9124306353127917</v>
+        <v>0.4740244892957276</v>
       </c>
       <c r="F151">
-        <v>0.8865018276259963</v>
+        <v>0.8332612148605943</v>
       </c>
       <c r="G151">
-        <v>1.144302272918077</v>
+        <v>1.088500038777212</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="O151">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="152">
@@ -9888,22 +9888,22 @@
         </is>
       </c>
       <c r="B152">
-        <v>1.278129394346296</v>
+        <v>1.008516346445382</v>
       </c>
       <c r="C152">
-        <v>0.7864748535863298</v>
+        <v>0.7963565723988284</v>
       </c>
       <c r="D152">
-        <v>0.3120221800397764</v>
+        <v>0.01064885661318577</v>
       </c>
       <c r="E152">
-        <v>0.7550236670085897</v>
+        <v>0.9915036022977319</v>
       </c>
       <c r="F152">
-        <v>0.2736063759996068</v>
+        <v>0.2117497949517643</v>
       </c>
       <c r="G152">
-        <v>5.970674998795996</v>
+        <v>4.803335093095293</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="O152">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="153">
@@ -9951,22 +9951,22 @@
         </is>
       </c>
       <c r="B153">
-        <v>0.6109061445337994</v>
+        <v>0.8548062801981527</v>
       </c>
       <c r="C153">
-        <v>0.7505151985990568</v>
+        <v>0.7046366405920725</v>
       </c>
       <c r="D153">
-        <v>-0.6566315274235501</v>
+        <v>-0.222640151742216</v>
       </c>
       <c r="E153">
-        <v>0.5114178717495266</v>
+        <v>0.8238155840971273</v>
       </c>
       <c r="F153">
-        <v>0.1403249183082968</v>
+        <v>0.2148225702249555</v>
       </c>
       <c r="G153">
-        <v>2.659586921042842</v>
+        <v>3.401382712724474</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="O153">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="154">
@@ -10014,22 +10014,22 @@
         </is>
       </c>
       <c r="B154">
-        <v>2.166521831611139</v>
+        <v>1.384465089842944</v>
       </c>
       <c r="C154">
-        <v>0.8001827607246702</v>
+        <v>0.8315339908778231</v>
       </c>
       <c r="D154">
-        <v>0.9661830734146978</v>
+        <v>0.3912213473980742</v>
       </c>
       <c r="E154">
-        <v>0.3339525812008005</v>
+        <v>0.6956336303207367</v>
       </c>
       <c r="F154">
-        <v>0.451488059384954</v>
+        <v>0.2713182410873554</v>
       </c>
       <c r="G154">
-        <v>10.39632554898993</v>
+        <v>7.064558495264253</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="O154">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="155">
@@ -10077,22 +10077,22 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.8229037135219485</v>
+        <v>0.7221017720153415</v>
       </c>
       <c r="C155">
-        <v>0.4446548329135918</v>
+        <v>0.4437335814299445</v>
       </c>
       <c r="D155">
-        <v>-0.4383536739672996</v>
+        <v>-0.7337492702350804</v>
       </c>
       <c r="E155">
-        <v>0.6611299229267691</v>
+        <v>0.463101563833169</v>
       </c>
       <c r="F155">
-        <v>0.3442374707866119</v>
+        <v>0.3026158711026849</v>
       </c>
       <c r="G155">
-        <v>1.967160983901086</v>
+        <v>1.723078724350059</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="O155">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="156">
@@ -10140,22 +10140,22 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.7269834792829459</v>
+        <v>0.8911177229009538</v>
       </c>
       <c r="C156">
-        <v>0.4725561416628605</v>
+        <v>0.450883869386518</v>
       </c>
       <c r="D156">
-        <v>-0.6747378736682335</v>
+        <v>-0.2556727876024609</v>
       </c>
       <c r="E156">
-        <v>0.4998423175434312</v>
+        <v>0.7982035092648037</v>
       </c>
       <c r="F156">
-        <v>0.2879280822191546</v>
+        <v>0.368249389685318</v>
       </c>
       <c r="G156">
-        <v>1.835545095417505</v>
+        <v>2.156394058783803</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="O156">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="157">
@@ -10203,22 +10203,22 @@
         </is>
       </c>
       <c r="B157">
-        <v>1.123559006079337</v>
+        <v>0.8001799457670159</v>
       </c>
       <c r="C157">
-        <v>0.4561588236257414</v>
+        <v>0.4878514718487436</v>
       </c>
       <c r="D157">
-        <v>0.2553964213887704</v>
+        <v>-0.4569395753878372</v>
       </c>
       <c r="E157">
-        <v>0.7984169344871603</v>
+        <v>0.647714477414683</v>
       </c>
       <c r="F157">
-        <v>0.4595288587876086</v>
+        <v>0.3075585021221267</v>
       </c>
       <c r="G157">
-        <v>2.747128533934914</v>
+        <v>2.08184114953667</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7727</v>
+        <v>7693</v>
       </c>
     </row>
   </sheetData>
